--- a/EUPlus/DataSheet.xlsx
+++ b/EUPlus/DataSheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://libertymutual-my.sharepoint.com/personal/mohammad_talib_libertymutual_com/Documents/Desktop/regression-pack/EUPlus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="114_{79F6D073-54D2-481B-9CDC-BBC4A16A047F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A15BF461-18DB-4204-8DC4-3F96AA09511F}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="114_{79F6D073-54D2-481B-9CDC-BBC4A16A047F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A91BCAB-FEA3-480B-B4D5-FECB707BD429}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{A2EF6AEE-92DE-49D8-BB60-1A120F6353A4}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2183" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2183" uniqueCount="677">
   <si>
     <t>First Named Insured</t>
   </si>
@@ -2082,6 +2082,9 @@
   </si>
   <si>
     <t>9/12/2026</t>
+  </si>
+  <si>
+    <t>https://n9971008:wm$qY@08@test5-underwritingplatform.grsazr.lmig.com</t>
   </si>
 </sst>
 </file>
@@ -8753,6 +8756,7 @@
     <col min="65" max="65" width="10" customWidth="1"/>
     <col min="66" max="66" width="23" bestFit="1" customWidth="1"/>
     <col min="67" max="67" width="42.7109375" customWidth="1"/>
+    <col min="70" max="70" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:71" x14ac:dyDescent="0.25">
@@ -9062,7 +9066,7 @@
     </row>
     <row r="3" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>592</v>
+        <v>676</v>
       </c>
       <c r="B3" t="s">
         <v>584</v>
@@ -9101,7 +9105,7 @@
         <v>673</v>
       </c>
       <c r="N3" t="s">
-        <v>674</v>
+        <v>472</v>
       </c>
       <c r="O3" t="s">
         <v>588</v>

--- a/EUPlus/DataSheet.xlsx
+++ b/EUPlus/DataSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://libertymutual-my.sharepoint.com/personal/mohammad_talib_libertymutual_com/Documents/Desktop/regression-pack/EUPlus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="114_{79F6D073-54D2-481B-9CDC-BBC4A16A047F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A91BCAB-FEA3-480B-B4D5-FECB707BD429}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="114_{79F6D073-54D2-481B-9CDC-BBC4A16A047F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFF783AE-F128-4618-B001-8D2FD516C125}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{A2EF6AEE-92DE-49D8-BB60-1A120F6353A4}"/>
   </bookViews>
@@ -2081,10 +2081,10 @@
     <t>ariz</t>
   </si>
   <si>
-    <t>9/12/2026</t>
-  </si>
-  <si>
-    <t>https://n9971008:wm$qY@08@test5-underwritingplatform.grsazr.lmig.com</t>
+    <t>01/1/2026</t>
+  </si>
+  <si>
+    <t>10/22/2026</t>
   </si>
 </sst>
 </file>
@@ -2527,6 +2527,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
@@ -9066,7 +9070,7 @@
     </row>
     <row r="3" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>676</v>
+        <v>592</v>
       </c>
       <c r="B3" t="s">
         <v>584</v>
@@ -9093,19 +9097,19 @@
         <v>123</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>608</v>
+        <v>675</v>
       </c>
       <c r="K3" t="s">
         <v>106</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>608</v>
+        <v>675</v>
       </c>
       <c r="M3" t="s">
         <v>673</v>
       </c>
       <c r="N3" t="s">
-        <v>472</v>
+        <v>674</v>
       </c>
       <c r="O3" t="s">
         <v>588</v>
@@ -9237,7 +9241,7 @@
         <v>120</v>
       </c>
       <c r="BF3" s="7" t="s">
-        <v>608</v>
+        <v>675</v>
       </c>
       <c r="BG3" t="s">
         <v>19</v>
@@ -9270,10 +9274,10 @@
         <v>1000</v>
       </c>
       <c r="BQ3" s="7" t="s">
-        <v>608</v>
+        <v>675</v>
       </c>
       <c r="BR3" s="7" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="BS3" s="16" t="s">
         <v>648</v>

--- a/EUPlus/DataSheet.xlsx
+++ b/EUPlus/DataSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://libertymutual-my.sharepoint.com/personal/mohammad_talib_libertymutual_com/Documents/Desktop/regression-pack/EUPlus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="114_{79F6D073-54D2-481B-9CDC-BBC4A16A047F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFF783AE-F128-4618-B001-8D2FD516C125}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="114_{79F6D073-54D2-481B-9CDC-BBC4A16A047F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D73AD389-B022-4316-BA69-BE5CE06CBED9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{A2EF6AEE-92DE-49D8-BB60-1A120F6353A4}"/>
   </bookViews>
@@ -2527,10 +2527,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>

--- a/EUPlus/DataSheet.xlsx
+++ b/EUPlus/DataSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://libertymutual-my.sharepoint.com/personal/mohammad_talib_libertymutual_com/Documents/Desktop/regression-pack/EUPlus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="114_{79F6D073-54D2-481B-9CDC-BBC4A16A047F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D73AD389-B022-4316-BA69-BE5CE06CBED9}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="114_{79F6D073-54D2-481B-9CDC-BBC4A16A047F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D2F24C8-7398-4112-800B-24E26ECECD9C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{A2EF6AEE-92DE-49D8-BB60-1A120F6353A4}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2183" uniqueCount="677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2183" uniqueCount="678">
   <si>
     <t>First Named Insured</t>
   </si>
@@ -2084,7 +2084,10 @@
     <t>01/1/2026</t>
   </si>
   <si>
-    <t>10/22/2026</t>
+    <t>https://n9971008:wm$qY@08@test5-underwritingplatform.grsazr.lmig.com</t>
+  </si>
+  <si>
+    <t>11/11/2026</t>
   </si>
 </sst>
 </file>
@@ -2527,6 +2530,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
@@ -9066,7 +9073,7 @@
     </row>
     <row r="3" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>592</v>
+        <v>676</v>
       </c>
       <c r="B3" t="s">
         <v>584</v>
@@ -9273,7 +9280,7 @@
         <v>675</v>
       </c>
       <c r="BR3" s="7" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="BS3" s="16" t="s">
         <v>648</v>
@@ -9504,10 +9511,10 @@
         <v>1000</v>
       </c>
       <c r="BQ9" s="7" t="s">
-        <v>608</v>
+        <v>675</v>
       </c>
       <c r="BR9" s="7" t="s">
-        <v>645</v>
+        <v>677</v>
       </c>
       <c r="BS9" s="16" t="s">
         <v>25</v>

--- a/EUPlus/DataSheet.xlsx
+++ b/EUPlus/DataSheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://libertymutual-my.sharepoint.com/personal/mohammad_talib_libertymutual_com/Documents/Desktop/regression-pack/EUPlus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="114_{79F6D073-54D2-481B-9CDC-BBC4A16A047F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D2F24C8-7398-4112-800B-24E26ECECD9C}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="114_{79F6D073-54D2-481B-9CDC-BBC4A16A047F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CB6C7C7-C95C-4BE6-8A55-DD87426A73B0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{A2EF6AEE-92DE-49D8-BB60-1A120F6353A4}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2183" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2183" uniqueCount="677">
   <si>
     <t>First Named Insured</t>
   </si>
@@ -2082,9 +2082,6 @@
   </si>
   <si>
     <t>01/1/2026</t>
-  </si>
-  <si>
-    <t>https://n9971008:wm$qY@08@test5-underwritingplatform.grsazr.lmig.com</t>
   </si>
   <si>
     <t>11/11/2026</t>
@@ -9073,7 +9070,7 @@
     </row>
     <row r="3" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>676</v>
+        <v>592</v>
       </c>
       <c r="B3" t="s">
         <v>584</v>
@@ -9280,7 +9277,7 @@
         <v>675</v>
       </c>
       <c r="BR3" s="7" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="BS3" s="16" t="s">
         <v>648</v>
@@ -9514,7 +9511,7 @@
         <v>675</v>
       </c>
       <c r="BR9" s="7" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="BS9" s="16" t="s">
         <v>25</v>

--- a/EUPlus/DataSheet.xlsx
+++ b/EUPlus/DataSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://libertymutual-my.sharepoint.com/personal/mohammad_talib_libertymutual_com/Documents/Desktop/regression-pack/EUPlus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="114_{79F6D073-54D2-481B-9CDC-BBC4A16A047F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CB6C7C7-C95C-4BE6-8A55-DD87426A73B0}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="114_{79F6D073-54D2-481B-9CDC-BBC4A16A047F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15499817-96F2-4FC5-B223-D1AEA095DBF5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{A2EF6AEE-92DE-49D8-BB60-1A120F6353A4}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2183" uniqueCount="677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2183" uniqueCount="678">
   <si>
     <t>First Named Insured</t>
   </si>
@@ -2085,6 +2085,9 @@
   </si>
   <si>
     <t>11/11/2026</t>
+  </si>
+  <si>
+    <t>https://n9971008:wm$qY@08@hfstage-underwritingplatform.grsazr.lmig.com</t>
   </si>
 </sst>
 </file>
@@ -9070,7 +9073,7 @@
     </row>
     <row r="3" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>592</v>
+        <v>677</v>
       </c>
       <c r="B3" t="s">
         <v>584</v>

--- a/EUPlus/DataSheet.xlsx
+++ b/EUPlus/DataSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://libertymutual-my.sharepoint.com/personal/mohammad_talib_libertymutual_com/Documents/Desktop/regression-pack/EUPlus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="114_{79F6D073-54D2-481B-9CDC-BBC4A16A047F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CB6C7C7-C95C-4BE6-8A55-DD87426A73B0}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="114_{79F6D073-54D2-481B-9CDC-BBC4A16A047F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB2F208A-3076-4514-89A8-E81565EAE175}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{A2EF6AEE-92DE-49D8-BB60-1A120F6353A4}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2183" uniqueCount="677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2183" uniqueCount="678">
   <si>
     <t>First Named Insured</t>
   </si>
@@ -2085,6 +2085,9 @@
   </si>
   <si>
     <t>11/11/2026</t>
+  </si>
+  <si>
+    <t>https://n9971008:wm$qY@08@test-underwritingplatform.grsazr.lmig.com</t>
   </si>
 </sst>
 </file>
@@ -9070,7 +9073,7 @@
     </row>
     <row r="3" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>592</v>
+        <v>677</v>
       </c>
       <c r="B3" t="s">
         <v>584</v>
